--- a/SuppXLS/Scen_ELC_IMP.xlsx
+++ b/SuppXLS/Scen_ELC_IMP.xlsx
@@ -4409,7 +4409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.42578125" customWidth="1" min="2" max="3"/>
@@ -4500,26 +4500,51 @@
       <c r="G6" s="8" t="n"/>
       <c r="H6" s="4" t="n"/>
     </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
+    <row r="7"/>
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
-          <t>FX</t>
+          <t>~TFM_UPD</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
-          <t>ACT_BND</t>
+          <t>Attribute</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
-          <t>2025,2030,2035,2040,2045,2050</t>
+          <t>AllRegions</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pset_Set</t>
+        </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Pset_PN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ACTCOST</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>IRE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>IMPNRGZ</t>
         </is>
